--- a/data/trans_bre/P1801_2016_2023-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1801_2016_2023-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,34</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 13,47</t>
+          <t>-4,36; 13,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 12,36</t>
+          <t>1,21; 14,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 31,32</t>
+          <t>-8,08; 30,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 20,15</t>
+          <t>1,83; 25,21</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 16,99</t>
+          <t>5,1; 17,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 11,92</t>
+          <t>-1,58; 9,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 39,02</t>
+          <t>10,72; 41,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 55,52</t>
+          <t>-4,96; 43,87</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 19,94</t>
+          <t>4,94; 20,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 11,37</t>
+          <t>-3,33; 10,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,45; 51,1</t>
+          <t>10,36; 51,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 18,68</t>
+          <t>-4,81; 16,43</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-9,3</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-18,02%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 13,29</t>
+          <t>-0,66; 14,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 2,69</t>
+          <t>-5,56; 12,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 25,84</t>
+          <t>-1,11; 27,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 4,84</t>
+          <t>-10,16; 28,12</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,83</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 18,01</t>
+          <t>-0,58; 17,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 15,85</t>
+          <t>3,18; 18,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 44,48</t>
+          <t>-1,18; 42,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 29,72</t>
+          <t>5,28; 35,92</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,35</t>
+          <t>8,8</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 15,55</t>
+          <t>-1,04; 15,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 15,87</t>
+          <t>2,32; 16,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 32,46</t>
+          <t>-1,81; 33,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 28,33</t>
+          <t>3,89; 30,05</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16,22</t>
+          <t>11,18</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,1; 18,94</t>
+          <t>8,16; 19,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 29,44</t>
+          <t>5,85; 16,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,24; 58,02</t>
+          <t>21,11; 59,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,39; 51,3</t>
+          <t>9,42; 29,83</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-7,9</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-15,46%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 17,63</t>
+          <t>7,12; 17,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 11,05</t>
+          <t>5,55; 14,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,03; 37,06</t>
+          <t>13,46; 36,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 33,85</t>
+          <t>15,47; 48,37</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 13,09</t>
+          <t>8,06; 13,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 11,92</t>
+          <t>5,59; 10,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,08; 28,89</t>
+          <t>16,93; 29,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 23,45</t>
+          <t>11,42; 22,67</t>
         </is>
       </c>
     </row>
